--- a/10.k/halozat/halozat-alapok/Dhcp-Alapok.xlsx
+++ b/10.k/halozat/halozat-alapok/Dhcp-Alapok.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\beni\Informatika\10.k\Halozat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D0783A5-5877-429F-B63E-79349532F92B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAACD5F9-CE03-4464-8854-193833B4B363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16690" yWindow="-370" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{BB618157-CA73-4FD7-978C-16B8EAACF7F5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="17020" windowHeight="10000" activeTab="1" xr2:uid="{BB618157-CA73-4FD7-978C-16B8EAACF7F5}"/>
   </bookViews>
   <sheets>
     <sheet name="IRODA" sheetId="1" r:id="rId1"/>
@@ -869,10 +869,10 @@
       <c r="F4" t="s">
         <v>31</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="3" t="s">
         <v>31</v>
       </c>
     </row>
